--- a/data-raw/data-tidy/hack-tianyan/hub/match-tianyan-tot36-2023-07-23-hand.xlsx
+++ b/data-raw/data-tidy/hack-tianyan/hub/match-tianyan-tot36-2023-07-23-hand.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\techme\data-raw\data-tidy\hack-tianyan\hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035076D4-F0CE-44E6-B15F-4EB84DEB3C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01982DFA-E0B4-4A84-B8E7-C20043856DE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-6360" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="164">
   <si>
     <t>index</t>
   </si>
@@ -512,6 +512,10 @@
   </si>
   <si>
     <t>四川</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -921,6 +925,12 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
